--- a/output/aveva_export/ALP_aveva_tag_export.xlsx
+++ b/output/aveva_export/ALP_aveva_tag_export.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-09-27T18:30:44Z by EPCE | aveva_export v1.0.0 | data 639393962f669c88 | class library source sha256 f3cb7e7762c96606</t>
+          <t>generated 2026-09-27T18:48:52Z by SETUP | aveva_export v1.0.0 | data 639393962f669c88 | class library source sha256 f3cb7e7762c96606</t>
         </is>
       </c>
     </row>

--- a/output/aveva_export/ALP_aveva_tag_export.xlsx
+++ b/output/aveva_export/ALP_aveva_tag_export.xlsx
@@ -454,7 +454,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-09-27T18:48:52Z by SETUP | aveva_export v1.0.0 | data 639393962f669c88 | class library source sha256 f3cb7e7762c96606</t>
+          <t>generated 2026-09-28T04:17:32Z by SETUP | aveva_export v1.0.0 | data 8d65452576ccc3c9 | class library source sha256 f3cb7e7762c96606</t>
         </is>
       </c>
     </row>

--- a/output/aveva_export/ALP_aveva_tag_export.xlsx
+++ b/output/aveva_export/ALP_aveva_tag_export.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-09-28T18:42:31Z by SETUP | aveva_export v1.0.0 | data f5d7ed91710919b2 | class library source sha256 f3cb7e7762c96606</t>
+          <t>generated 2026-09-28T19:00:21Z by EPCE | aveva_export v1.0.0 | data e326e33dda742afe | class library source sha256 f3cb7e7762c96606</t>
         </is>
       </c>
     </row>

--- a/output/aveva_export/ALP_aveva_tag_export.xlsx
+++ b/output/aveva_export/ALP_aveva_tag_export.xlsx
@@ -476,7 +476,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-09-28T19:00:21Z by EPCE | aveva_export v1.0.0 | data e326e33dda742afe | class library source sha256 f3cb7e7762c96606</t>
+          <t>generated 2026-09-29T02:51:51Z by SETUP | aveva_export v1.0.0 | data 0c0142d5893ca067 | class library source sha256 f3cb7e7762c96606</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10">
@@ -779,7 +779,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -839,7 +839,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -1059,7 +1059,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="33">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BFP maintenance hoist 10 t</t>
+          <t>BFP maintenance hoist 16 t</t>
         </is>
       </c>
     </row>
@@ -42780,7 +42780,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chemical dosing skid (ammonia, oxygen scavenger)</t>
+          <t>Chemical dosing skid (ammonia, phosphate / caustic trim, lay-up dosing)</t>
         </is>
       </c>
     </row>
@@ -43667,7 +43667,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44091,7 +44091,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00GMA10AT001</t>
+          <t>00GKA10AT002</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -44106,14 +44106,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Oil separator (API / coalescing)</t>
+          <t>Potable water remineralisation filter (calcite)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00LDA10AT001</t>
+          <t>00GMA10AT001</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -44128,14 +44128,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Condensate polisher vessel A</t>
+          <t>Oil separator (API / coalescing)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00LDA10AT002</t>
+          <t>00LDA10AT001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -44150,14 +44150,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Condensate polisher vessel B</t>
+          <t>Condensate polisher vessel A</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00PAA10AT001</t>
+          <t>00LDA10AT002</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -44172,14 +44172,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Travelling band screen A</t>
+          <t>Condensate polisher vessel B</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00PAA10AT002</t>
+          <t>00PAA10AT001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -44194,14 +44194,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Travelling band screen B</t>
+          <t>Travelling band screen A</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00PAA10AT003</t>
+          <t>00PAA10AT002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -44216,14 +44216,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Trash rake A</t>
+          <t>Travelling band screen B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00PAA10AT004</t>
+          <t>00PAA10AT003</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -44238,14 +44238,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Trash rake B</t>
+          <t>Trash rake A</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00PAH10AT001</t>
+          <t>00PAA10AT004</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -44260,14 +44260,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Debris filter A</t>
+          <t>Trash rake B</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00PAH10AT002</t>
+          <t>00PAH10AT001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -44282,14 +44282,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Debris filter B</t>
+          <t>Debris filter A</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00PBA10AT001</t>
+          <t>00PAH10AT002</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -44304,14 +44304,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Electrolyser cell stack A</t>
+          <t>Debris filter B</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00PBA10AT002</t>
+          <t>00PBA10AT001</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -44326,14 +44326,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Electrolyser cell stack B</t>
+          <t>Electrolyser cell stack A</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00PGA10AT001</t>
+          <t>00PBA10AT002</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -44348,27 +44348,49 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>CCW side-stream filter</t>
+          <t>Electrolyser cell stack B</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>00PGA10AT001</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Filter</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CCW side-stream filter</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>00QEA10AT003</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Filter</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>Instrument air after-filters</t>
         </is>
@@ -44450,7 +44472,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LDO storage tank A 3,500 m3</t>
+          <t>LDO storage tank A 3,800 m3</t>
         </is>
       </c>
     </row>
@@ -44472,7 +44494,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LDO storage tank B 3,500 m3</t>
+          <t>LDO storage tank B 3,800 m3</t>
         </is>
       </c>
     </row>
@@ -44589,7 +44611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44654,7 +44676,29 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Instrument air dryer (2 x 100 %)</t>
+          <t>Instrument air dryer A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00QEA10AT002</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Instrument Air Dryer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Instrument air dryer B</t>
         </is>
       </c>
     </row>
@@ -44734,7 +44778,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Gas preheater A (electric)</t>
+          <t>Gas preheater A (indirect water-bath, gas-fired)</t>
         </is>
       </c>
     </row>
@@ -44756,7 +44800,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Gas preheater B (electric)</t>
+          <t>Gas preheater B (indirect water-bath, gas-fired)</t>
         </is>
       </c>
     </row>
@@ -44917,7 +44961,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44982,7 +45026,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.4 kV 2.5 MVA, A</t>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - power block, A</t>
         </is>
       </c>
     </row>
@@ -45004,7 +45048,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.4 kV 2.5 MVA, B</t>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - power block, B</t>
         </is>
       </c>
     </row>
@@ -45026,7 +45070,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.4 kV 1.6 MVA - CW pump house</t>
+          <t>LV transformer 10.5/0.42 kV 2.0 MVA - BOP and water treatment, A</t>
         </is>
       </c>
     </row>
@@ -45048,14 +45092,14 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.4 kV 1.6 MVA - water treatment</t>
+          <t>LV transformer 10.5/0.42 kV 2.0 MVA - BOP and water treatment, B</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10BAT10</t>
+          <t>00BFT50</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -45070,14 +45114,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GT step-up transformer 560 MVA 400/21 kV</t>
+          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, A</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10BBT10</t>
+          <t>00BFT60</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -45092,14 +45136,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GT unit auxiliary transformer 21/10.5 kV 31.5 MVA</t>
+          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, B</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20BAT10</t>
+          <t>10BAT10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -45114,27 +45158,71 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>ST step-up transformer 270 MVA 400/15.75 kV</t>
+          <t>GT step-up transformer 560 MVA 400/21 kV</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>10BBT10</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>GT unit auxiliary transformer 21/10.5 kV 31.5 MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>20BAT10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ST step-up transformer 270 MVA 400/15.75 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>20BBT10</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Power Transformer</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>ST unit auxiliary transformer 15.75/10.5 kV 16 MVA</t>
         </is>
@@ -46880,7 +46968,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>6 items</t>
         </is>
       </c>
     </row>
@@ -48178,7 +48266,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>6 items</t>
         </is>
       </c>
     </row>
@@ -48574,7 +48662,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Potable Water: Filter - Datasheet</t>
+          <t>2 items</t>
         </is>
       </c>
     </row>
@@ -48596,7 +48684,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>2 items</t>
+          <t>3 items</t>
         </is>
       </c>
     </row>
@@ -48838,7 +48926,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>4 items</t>
+          <t>6 items</t>
         </is>
       </c>
     </row>
@@ -48860,7 +48948,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>2 items</t>
+          <t>4 items</t>
         </is>
       </c>
     </row>
@@ -50224,7 +50312,7 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>2 items</t>
+          <t>3 items</t>
         </is>
       </c>
     </row>
@@ -57935,7 +58023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -58205,7 +58293,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>00PBA10BB001</t>
+          <t>00GNA10BB003</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -58220,14 +58308,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Hypochlorite storage tank A</t>
+          <t>Sulphuric acid tank (neutralisation)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00PBA10BB002</t>
+          <t>00GNA10BB004</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -58242,14 +58330,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Hypochlorite storage tank B</t>
+          <t>Caustic tank (neutralisation)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00PGA10BB002</t>
+          <t>00PBA10BB001</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -58264,14 +58352,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>CCW chemical pot feeder</t>
+          <t>Hypochlorite storage tank A</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00QCA10BB001</t>
+          <t>00PBA10BB002</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -58286,14 +58374,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Ammonia solution tank</t>
+          <t>Hypochlorite storage tank B</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00QCA10BB002</t>
+          <t>00PGA10BB002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -58308,14 +58396,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Oxygen scavenger tank</t>
+          <t>CCW chemical pot feeder</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00QCA10BB003</t>
+          <t>00QCA10BB001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -58330,14 +58418,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Caustic solution tank</t>
+          <t>Ammonia solution tank</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00QEA10BB002</t>
+          <t>00QCA10BB002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -58352,14 +58440,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Service air receiver</t>
+          <t>Oxygen scavenger tank</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00QHA10BB001</t>
+          <t>00QCA10BB003</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -58374,14 +58462,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Auxiliary boiler feed water tank / deaerator</t>
+          <t>Caustic solution tank</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00QHA10BB002</t>
+          <t>00QEA10BB002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -58396,14 +58484,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Auxiliary boiler blowdown vessel</t>
+          <t>Service air receiver</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00QJA10BB001</t>
+          <t>00QHA10BB001</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -58418,14 +58506,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Nitrogen buffer vessel</t>
+          <t>Auxiliary boiler feed water tank / deaerator</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00SGA10BB002</t>
+          <t>00QHA10BB002</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -58440,14 +58528,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fire water tank B</t>
+          <t>Auxiliary boiler blowdown vessel</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00SGC10BB001</t>
+          <t>00QJA10BB001</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -58462,14 +58550,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Foam concentrate tank</t>
+          <t>Nitrogen buffer vessel</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00XJA10BB001</t>
+          <t>00SGA10BB002</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -58484,14 +58572,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Emergency diesel generator day tank</t>
+          <t>Fire water tank B</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10HAN10BB001</t>
+          <t>00SGC10BB001</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -58506,14 +58594,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>HRSG blowdown tank</t>
+          <t>Foam concentrate tank</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10HAN10BB002</t>
+          <t>00XJA10BB001</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -58528,14 +58616,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Atmospheric drain tank</t>
+          <t>Emergency diesel generator day tank</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10HSB10BB001</t>
+          <t>10HAN10BB001</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -58550,27 +58638,71 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Aqueous ammonia tank A 30 m3</t>
+          <t>HRSG blowdown tank</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>10HAN10BB002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Atmospheric drain tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10HSB10BB001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Aqueous ammonia tank A 30 m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>10HSB10BB002</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Tank</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>Aqueous ammonia tank B 30 m3</t>
         </is>
@@ -59193,7 +59325,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D67"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -59485,7 +59617,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>00GCA10AP001</t>
+          <t>00GBA10AP005</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -59500,14 +59632,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>EDI feed pump A</t>
+          <t>SWRO energy recovery device and booster pump A</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>00GCA10AP002</t>
+          <t>00GBA10AP006</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -59522,14 +59654,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>EDI feed pump B</t>
+          <t>SWRO energy recovery device and booster pump B</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>00GHA10AP001</t>
+          <t>00GCA10AP001</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -59544,14 +59676,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Demin water forwarding pump A</t>
+          <t>EDI feed pump A</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>00GHA10AP002</t>
+          <t>00GCA10AP002</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -59566,14 +59698,14 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Demin water forwarding pump B</t>
+          <t>EDI feed pump B</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>00GKA10AP001</t>
+          <t>00GHA10AP001</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -59588,14 +59720,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Potable water pump A</t>
+          <t>Demin water forwarding pump A</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>00GKA10AP002</t>
+          <t>00GHA10AP002</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -59610,14 +59742,14 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Potable water pump B</t>
+          <t>Demin water forwarding pump B</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>00GMA10AP001</t>
+          <t>00GKA10AP001</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -59632,14 +59764,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Process drain sump pump - power block A</t>
+          <t>Potable water pump A</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>00GMA10AP002</t>
+          <t>00GKA10AP002</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -59654,14 +59786,14 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Process drain sump pump - power block B</t>
+          <t>Potable water pump B</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>00GMA10AP003</t>
+          <t>00GKA10AP003</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -59676,14 +59808,14 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Oily water sump pump - transformer area</t>
+          <t>Potable water hypochlorite dosing pump</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>00GMA10AP004</t>
+          <t>00GMA10AP001</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -59698,14 +59830,14 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Oily water sump pump - LDO area</t>
+          <t>Process drain sump pump - power block A</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>00GMA10AP005</t>
+          <t>00GMA10AP002</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -59720,14 +59852,14 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Chemical drain sump pump - water treatment</t>
+          <t>Process drain sump pump - power block B</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>00GMA10AP006</t>
+          <t>00GMA10AP003</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -59742,14 +59874,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Drain sump pump - CW pump house</t>
+          <t>Oily water sump pump - transformer area</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>00GNA10AP001</t>
+          <t>00GMA10AP004</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -59764,14 +59896,14 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Waste water transfer pump A</t>
+          <t>Oily water sump pump - LDO area</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>00GNA10AP002</t>
+          <t>00GMA10AP005</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -59786,14 +59918,14 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Waste water transfer pump B</t>
+          <t>Chemical drain sump pump - water treatment</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>00GNA10AP003</t>
+          <t>00GMA10AP006</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -59808,14 +59940,14 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Treated effluent pump A</t>
+          <t>Drain sump pump - CW pump house</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>00GNA10AP004</t>
+          <t>00GNA10AP001</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -59830,14 +59962,14 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Treated effluent pump B</t>
+          <t>Waste water transfer pump A</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>00GUA10AP001</t>
+          <t>00GNA10AP002</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -59852,14 +59984,14 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sanitary lift pump A</t>
+          <t>Waste water transfer pump B</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>00GUA10AP002</t>
+          <t>00GNA10AP003</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -59874,14 +60006,14 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Sanitary lift pump B</t>
+          <t>Treated effluent pump A</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>00PAA10AP001</t>
+          <t>00GNA10AP004</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -59896,14 +60028,14 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Screen wash pump A</t>
+          <t>Treated effluent pump B</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>00PAA10AP002</t>
+          <t>00GNA10AP005</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -59918,14 +60050,14 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Screen wash pump B</t>
+          <t>Neutralisation acid dosing pump</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>00PAC10AP001</t>
+          <t>00GNA10AP006</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -59940,14 +60072,14 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>CW pump A (2 x 50 %, vertical)</t>
+          <t>Neutralisation caustic dosing pump</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>00PAC10AP002</t>
+          <t>00GUA10AP001</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -59962,14 +60094,14 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>CW pump B (2 x 50 %, vertical)</t>
+          <t>Sanitary lift pump A</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>00PAH10AP001</t>
+          <t>00GUA10AP002</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -59984,14 +60116,14 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ball recirculation pump A</t>
+          <t>Sanitary lift pump B</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>00PAH10AP002</t>
+          <t>00PAA10AP001</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -60006,14 +60138,14 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ball recirculation pump B</t>
+          <t>Screen wash pump A</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>00PBA10AP001</t>
+          <t>00PAA10AP002</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -60028,14 +60160,14 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Chlorination seawater booster pump A</t>
+          <t>Screen wash pump B</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>00PBA10AP002</t>
+          <t>00PAC10AP001</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -60050,14 +60182,14 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Chlorination seawater booster pump B</t>
+          <t>CW pump A (2 x 50 %, vertical)</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>00PBA10AP003</t>
+          <t>00PAC10AP002</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -60072,14 +60204,14 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Hypochlorite dosing pump A</t>
+          <t>CW pump B (2 x 50 %, vertical)</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>00PBA10AP004</t>
+          <t>00PAH10AP001</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -60094,14 +60226,14 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Hypochlorite dosing pump B</t>
+          <t>Ball recirculation pump A</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>00PGA10AP001</t>
+          <t>00PAH10AP002</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -60116,14 +60248,14 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>CCW pump A (2 x 100 %)</t>
+          <t>Ball recirculation pump B</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>00PGA10AP002</t>
+          <t>00PBA10AP001</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -60138,14 +60270,14 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>CCW pump B (2 x 100 %)</t>
+          <t>Chlorination seawater booster pump A</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>00QCA10AP001</t>
+          <t>00PBA10AP002</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -60160,14 +60292,14 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Ammonia dosing pump A</t>
+          <t>Chlorination seawater booster pump B</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>00QCA10AP002</t>
+          <t>00PBA10AP003</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -60182,14 +60314,14 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Ammonia dosing pump B</t>
+          <t>Hypochlorite dosing pump A</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>00QCA10AP003</t>
+          <t>00PBA10AP004</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -60204,14 +60336,14 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Oxygen scavenger dosing pump A</t>
+          <t>Hypochlorite dosing pump B</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>00QCA10AP004</t>
+          <t>00PGA10AP001</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -60226,14 +60358,14 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Oxygen scavenger dosing pump B</t>
+          <t>CCW pump A (2 x 100 %)</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>00QCA10AP005</t>
+          <t>00PGA10AP002</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -60248,14 +60380,14 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Phosphate / caustic dosing pump A</t>
+          <t>CCW pump B (2 x 100 %)</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>00QCA10AP006</t>
+          <t>00QCA10AP001</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -60270,14 +60402,14 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Phosphate / caustic dosing pump B</t>
+          <t>Ammonia dosing pump A</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>00QHA10AP001</t>
+          <t>00QCA10AP002</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -60292,14 +60424,14 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Auxiliary boiler feed pump A</t>
+          <t>Ammonia dosing pump B</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>00QHA10AP002</t>
+          <t>00QCA10AP003</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -60314,14 +60446,14 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Auxiliary boiler feed pump B</t>
+          <t>Oxygen scavenger dosing pump A</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>00SAA10AP001</t>
+          <t>00QCA10AP004</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -60336,14 +60468,14 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Chilled water pump A</t>
+          <t>Oxygen scavenger dosing pump B</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>00SAA10AP002</t>
+          <t>00QCA10AP005</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -60358,14 +60490,14 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Chilled water pump B</t>
+          <t>Phosphate / caustic dosing pump A</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>00SGA10AP001</t>
+          <t>00QCA10AP006</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -60380,14 +60512,14 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Electric fire pump</t>
+          <t>Phosphate / caustic dosing pump B</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>00SGA10AP002</t>
+          <t>00QHA10AP001</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -60402,14 +60534,14 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Diesel fire pump</t>
+          <t>Auxiliary boiler feed pump A</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>00SGA10AP003</t>
+          <t>00QHA10AP002</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -60424,14 +60556,14 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Jockey pump</t>
+          <t>Auxiliary boiler feed pump B</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10HAN10AP001</t>
+          <t>00SAA10AP001</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -60446,14 +60578,14 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>HRSG drain pump A</t>
+          <t>Chilled water pump A</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10HAN10AP002</t>
+          <t>00SAA10AP002</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -60468,14 +60600,14 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>HRSG drain pump B</t>
+          <t>Chilled water pump B</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10HSB10AP001</t>
+          <t>00SGA10AP001</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -60490,14 +60622,14 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Ammonia forwarding pump A</t>
+          <t>Electric fire pump</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10HSB10AP002</t>
+          <t>00SGA10AP002</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -60512,14 +60644,14 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Ammonia forwarding pump B</t>
+          <t>Diesel fire pump</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10LAC10AP001</t>
+          <t>00SGA10AP003</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -60534,14 +60666,14 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Boiler feed pump A (2 x 100 %, VFD)</t>
+          <t>Jockey pump</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10LAC10AP002</t>
+          <t>10HAN10AP001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -60556,14 +60688,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Boiler feed pump B (2 x 100 %, VFD)</t>
+          <t>HRSG drain pump A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>20LCB10AP001</t>
+          <t>10HAN10AP002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -60578,14 +60710,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Condensate extraction pump A (2 x 100 %)</t>
+          <t>HRSG drain pump B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>20LCB10AP002</t>
+          <t>10HSB10AP001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -60600,14 +60732,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Condensate extraction pump B (2 x 100 %)</t>
+          <t>Ammonia forwarding pump A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>20MAJ10AP001</t>
+          <t>10HSB10AP002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -60622,27 +60754,137 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Condenser vacuum pump A</t>
+          <t>Ammonia forwarding pump B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>10LAC10AP001</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Boiler feed pump A (2 x 100 %, VFD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>10LAC10AP002</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>Boiler feed pump B (2 x 100 %, VFD)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>20LCB10AP001</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>Condensate extraction pump A (2 x 100 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>20LCB10AP002</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Condensate extraction pump B (2 x 100 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>20MAJ10AP001</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Condenser vacuum pump A</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
           <t>20MAJ10AP002</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B72" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C72" t="inlineStr">
         <is>
           <t>Centrifugal Pump</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D72" t="inlineStr">
         <is>
           <t>Condenser vacuum pump B</t>
         </is>

--- a/output/aveva_export/ALP_aveva_tag_export.xlsx
+++ b/output/aveva_export/ALP_aveva_tag_export.xlsx
@@ -16,27 +16,30 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Compressor" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Condenser" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Cabinet" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crane" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deliverables Documents" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drawing" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Package Skid" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fan" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Roof Tank" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gas Turbine" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument Air Dryer" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plate Heat Exchanger" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Transformer" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure Vessel" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specification Documents" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steam Generator" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steam Turbine" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switchgear And Controlgear" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synchronous Generator" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tank" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UPS Unit" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Control Panel" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crane" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Deliverables Documents" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drawing" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Equipment Package Skid" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fan" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Filter" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fixed Roof Tank" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Gas Turbine" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrument Air Dryer" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plate Heat Exchanger" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Power Transformer" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pressure Vessel" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Specification Documents" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stack" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steam Generator" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Steam Turbine" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Switchgear And Controlgear" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Synchronous Generator" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="System" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tank" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Transformer" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UPS Unit" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Valve" sheetId="33" state="visible" r:id="rId33"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,7 +460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -476,7 +479,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>generated 2026-09-29T02:51:51Z by SETUP | aveva_export v1.0.0 | data 0c0142d5893ca067 | class library source sha256 f3cb7e7762c96606</t>
+          <t>generated 2026-09-29T03:49:35Z by EPCE | aveva_export v1.0.0 | data 594b3969f57fee54 | class library source sha256 f3cb7e7762c96606</t>
         </is>
       </c>
     </row>
@@ -599,7 +602,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
@@ -665,297 +668,297 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Crane</t>
+          <t>Control Panel</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Crane</t>
+          <t>Control Panel</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000296</t>
+          <t>AVEVA-1.0.1-CLA-000271</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Deliverables Documents</t>
+          <t>Crane</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Deliverables Documents</t>
+          <t>Crane</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000342</t>
+          <t>AVEVA-1.0.1-CLA-000296</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1178</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Deliverables Documents</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Drawing</t>
+          <t>Deliverables Documents</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000396</t>
+          <t>AVEVA-1.0.1-CLA-000342</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>690</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Equipment Package Skid</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Equipment Package Skid</t>
+          <t>Drawing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000474</t>
+          <t>AVEVA-1.0.1-CLA-000396</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>27</v>
+        <v>690</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>Equipment Package Skid</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Fan</t>
+          <t>Equipment Package Skid</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000491</t>
+          <t>AVEVA-1.0.1-CLA-000474</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Filter</t>
+          <t>Fan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000502</t>
+          <t>AVEVA-1.0.1-CLA-000491</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Fixed Roof Tank</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fixed Roof Tank</t>
+          <t>Filter</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000515</t>
+          <t>AVEVA-1.0.1-CLA-000502</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gas Turbine</t>
+          <t>Fixed Roof Tank</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Gas Turbine</t>
+          <t>Fixed Roof Tank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000569</t>
+          <t>AVEVA-1.0.1-CLA-000515</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Instrument Air Dryer</t>
+          <t>Gas Turbine</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Instrument Air Dryer</t>
+          <t>Gas Turbine</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000679</t>
+          <t>AVEVA-1.0.1-CLA-000569</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Plate Heat Exchanger</t>
+          <t>Instrument Air Dryer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Plate Heat Exchanger</t>
+          <t>Instrument Air Dryer</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000949</t>
+          <t>AVEVA-1.0.1-CLA-000679</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000978</t>
+          <t>AVEVA-1.0.1-CLA-000949</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pressure Vessel</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Pressure Vessel</t>
+          <t>Power Transformer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000996</t>
+          <t>AVEVA-1.0.1-CLA-000978</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specification Documents</t>
+          <t>Pressure Vessel</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Specification Documents</t>
+          <t>Pressure Vessel</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001199</t>
+          <t>AVEVA-1.0.1-CLA-000996</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>412</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Stack</t>
+          <t>Specification Documents</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Stack</t>
+          <t>Specification Documents</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001212</t>
+          <t>AVEVA-1.0.1-CLA-001199</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Steam Generator</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Steam Generator</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001230</t>
+          <t>AVEVA-1.0.1-CLA-001212</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -965,17 +968,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Steam Turbine</t>
+          <t>Steam Generator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Steam Turbine</t>
+          <t>Steam Generator</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001234</t>
+          <t>AVEVA-1.0.1-CLA-001230</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -985,101 +988,161 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Switchgear And Controlgear</t>
+          <t>Steam Turbine</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Switchgear And Controlgear</t>
+          <t>Steam Turbine</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001260</t>
+          <t>AVEVA-1.0.1-CLA-001234</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Synchronous Generator</t>
+          <t>Switchgear And Controlgear</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Synchronous Generator</t>
+          <t>Switchgear And Controlgear</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001265</t>
+          <t>AVEVA-1.0.1-CLA-001260</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Synchronous Generator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>System</t>
+          <t>Synchronous Generator</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001269</t>
+          <t>AVEVA-1.0.1-CLA-001265</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>System</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>System</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001272</t>
+          <t>AVEVA-1.0.1-CLA-001269</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>29</v>
+        <v>119</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001272</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001318</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>UPS Unit</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>UPS Unit</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>AVEVA-1.0.1-CLA-001465</t>
         </is>
       </c>
-      <c r="D33" t="n">
+      <c r="D35" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001471</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1088,6 +1151,108 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-000271</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10MKA30</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GT generator protection panels (main 1 / main 2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>20MKA30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Control Panel</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ST generator protection panels (main 1 / main 2)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1277,7 +1442,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -27251,7 +27416,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -42489,7 +42654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43141,7 +43306,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -43661,7 +43826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44401,7 +44566,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44525,7 +44690,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44605,7 +44770,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -44699,174 +44864,6 @@
       <c r="D5" t="inlineStr">
         <is>
           <t>Instrument air dryer B</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AVEVA-1.0.1-CLA-000949</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00EKA10AC001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Plate Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Gas preheater A (indirect water-bath, gas-fired)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00EKA10AC002</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Plate Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Gas preheater B (indirect water-bath, gas-fired)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00PGA10AC001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Plate Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CCW plate heat exchanger A (2 x 100 %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00PGA10AC002</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Plate Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CCW plate heat exchanger B (2 x 100 %)</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00QUA10AC001</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Plate Heat Exchanger</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Sample cooler rack</t>
         </is>
       </c>
     </row>
@@ -44961,7 +44958,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -44997,7 +44994,7 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-000978</t>
+          <t>AVEVA-1.0.1-CLA-000949</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -45011,7 +45008,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00BFT10</t>
+          <t>00EKA10AC001</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -45021,19 +45018,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.42 kV 3.15 MVA - power block, A</t>
+          <t>Gas preheater A (indirect water-bath, gas-fired)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>00BFT20</t>
+          <t>00EKA10AC002</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -45043,19 +45040,19 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.42 kV 3.15 MVA - power block, B</t>
+          <t>Gas preheater B (indirect water-bath, gas-fired)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>00BFT30</t>
+          <t>00PGA10AC001</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -45065,19 +45062,19 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.42 kV 2.0 MVA - BOP and water treatment, A</t>
+          <t>CCW plate heat exchanger A (2 x 100 %)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>00BFT40</t>
+          <t>00PGA10AC002</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -45087,19 +45084,19 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.42 kV 2.0 MVA - BOP and water treatment, B</t>
+          <t>CCW plate heat exchanger B (2 x 100 %)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>00BFT50</t>
+          <t>00QUA10AC001</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -45109,122 +45106,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Power Transformer</t>
+          <t>Plate Heat Exchanger</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00BFT60</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Power Transformer</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>10BAT10</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Power Transformer</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>GT step-up transformer 560 MVA 400/21 kV</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10BBT10</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Power Transformer</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>GT unit auxiliary transformer 21/10.5 kV 31.5 MVA</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>20BAT10</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Power Transformer</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ST step-up transformer 270 MVA 400/15.75 kV</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>20BBT10</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Power Transformer</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>ST unit auxiliary transformer 15.75/10.5 kV 16 MVA</t>
+          <t>Sample cooler rack</t>
         </is>
       </c>
     </row>
@@ -45234,6 +45121,328 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-000978</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00BFT10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - GT and HRSG, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00BFT20</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - GT and HRSG, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00BFT30</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - BOP, fuel and buildings, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00BFT40</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 3.15 MVA - BOP, fuel and buildings, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00BFT50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00BFT60</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 1.0 MVA - CW intake, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00BFT70</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 1.6 MVA - ST and cooling, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00BFT80</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LV transformer 10.5/0.42 kV 1.6 MVA - ST and cooling, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>10BAT10</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>GT step-up transformer 560 MVA 400/21 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10BBT10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>GT unit auxiliary transformer 21/10.5 kV 31.5 MVA</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20BAT10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ST step-up transformer 270 MVA 400/15.75 kV</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>20BBT10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Power Transformer</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ST unit auxiliary transformer 15.75/10.5 kV 16 MVA</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -45335,13 +45544,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D415"/>
+  <dimension ref="A1:D416"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -46902,7 +47111,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>8 items</t>
+          <t>12 items</t>
         </is>
       </c>
     </row>
@@ -46968,7 +47177,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>6 items</t>
+          <t>8 items</t>
         </is>
       </c>
     </row>
@@ -53399,7 +53608,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ALP-IEC-20MAA-ME-DSH-0001</t>
+          <t>ALP-IEC-20MAA-IC-DSH-0003</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -53421,7 +53630,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>ALP-IEC-20MAG-ME-DSH-0001</t>
+          <t>ALP-IEC-20MAA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -53436,14 +53645,14 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>Seawater-Cooled Surface Condenser - Datasheet</t>
+          <t>IEC</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ALP-M01-10LAC-IC-DSH-0001</t>
+          <t>ALP-IEC-20MAG-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -53458,14 +53667,14 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>Boiler Feed Pumps - Supplier Instrument List and Datasheets</t>
+          <t>Seawater-Cooled Surface Condenser - Datasheet</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>ALP-M01-10LAC-ME-DSH-0001</t>
+          <t>ALP-M01-10LAC-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -53480,14 +53689,14 @@
       </c>
       <c r="D371" t="inlineStr">
         <is>
-          <t>Boiler Feed Pumps - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Boiler Feed Pumps - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>ALP-M02-20LCB-IC-DSH-0001</t>
+          <t>ALP-M01-10LAC-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -53502,14 +53711,14 @@
       </c>
       <c r="D372" t="inlineStr">
         <is>
-          <t>Condensate Extraction Pumps - Supplier Instrument List and Datasheets</t>
+          <t>Boiler Feed Pumps - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>ALP-M02-20LCB-ME-DSH-0001</t>
+          <t>ALP-M02-20LCB-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -53524,14 +53733,14 @@
       </c>
       <c r="D373" t="inlineStr">
         <is>
-          <t>Condensate Extraction Pumps - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Condensate Extraction Pumps - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>ALP-M03-00PAC-IC-DSH-0001</t>
+          <t>ALP-M02-20LCB-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -53546,14 +53755,14 @@
       </c>
       <c r="D374" t="inlineStr">
         <is>
-          <t>CW Pumps - Supplier Instrument List and Datasheets</t>
+          <t>Condensate Extraction Pumps - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>ALP-M03-00PAC-ME-DSH-0001</t>
+          <t>ALP-M03-00PAC-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -53568,14 +53777,14 @@
       </c>
       <c r="D375" t="inlineStr">
         <is>
-          <t>CW Pumps - Supplier Certified Datasheets and Performance Curves</t>
+          <t>CW Pumps - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>ALP-M04-00PAA-IC-DSH-0001</t>
+          <t>ALP-M03-00PAC-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -53590,14 +53799,14 @@
       </c>
       <c r="D376" t="inlineStr">
         <is>
-          <t>Travelling Band Screens and Trash Rakes - Supplier Instrument List and Datasheets</t>
+          <t>CW Pumps - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>ALP-M04-00PAA-ME-DSH-0001</t>
+          <t>ALP-M04-00PAA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -53612,14 +53821,14 @@
       </c>
       <c r="D377" t="inlineStr">
         <is>
-          <t>Travelling Band Screens and Trash Rakes - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Travelling Band Screens and Trash Rakes - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>ALP-M05-00PBA-IC-DSH-0001</t>
+          <t>ALP-M04-00PAA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -53634,14 +53843,14 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>Electro-Chlorination Package - Supplier Instrument List and Datasheets</t>
+          <t>Travelling Band Screens and Trash Rakes - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>ALP-M05-00PBA-ME-DSH-0001</t>
+          <t>ALP-M05-00PBA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -53656,14 +53865,14 @@
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Electro-Chlorination Package - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Electro-Chlorination Package - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>ALP-M06-00PAH-IC-DSH-0001</t>
+          <t>ALP-M05-00PBA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -53678,14 +53887,14 @@
       </c>
       <c r="D380" t="inlineStr">
         <is>
-          <t>Condenser Tube Cleaning System - Supplier Instrument List and Datasheets</t>
+          <t>Electro-Chlorination Package - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>ALP-M06-00PAH-ME-DSH-0001</t>
+          <t>ALP-M06-00PAH-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -53700,14 +53909,14 @@
       </c>
       <c r="D381" t="inlineStr">
         <is>
-          <t>Condenser Tube Cleaning System - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Condenser Tube Cleaning System - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>ALP-M07-00PGA-IC-DSH-0001</t>
+          <t>ALP-M06-00PAH-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -53722,14 +53931,14 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>Closed Cooling Water Heat Exchangers, Pumps, Tank - Supplier Instrument List and Datasheets</t>
+          <t>Condenser Tube Cleaning System - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>ALP-M07-00PGA-ME-DSH-0001</t>
+          <t>ALP-M07-00PGA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -53744,14 +53953,14 @@
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Closed Cooling Water Heat Exchangers, Pumps, Tank - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Closed Cooling Water Heat Exchangers, Pumps, Tank - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>ALP-M08-00QEA-IC-DSH-0001</t>
+          <t>ALP-M07-00PGA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -53766,14 +53975,14 @@
       </c>
       <c r="D384" t="inlineStr">
         <is>
-          <t>Air Compressors and Dryers - Supplier Instrument List and Datasheets</t>
+          <t>Closed Cooling Water Heat Exchangers, Pumps, Tank - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>ALP-M08-00QEA-ME-DSH-0001</t>
+          <t>ALP-M08-00QEA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -53788,14 +53997,14 @@
       </c>
       <c r="D385" t="inlineStr">
         <is>
-          <t>Air Compressors and Dryers - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Air Compressors and Dryers - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>ALP-M09-00QHA-IC-DSH-0001</t>
+          <t>ALP-M08-00QEA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -53810,14 +54019,14 @@
       </c>
       <c r="D386" t="inlineStr">
         <is>
-          <t>Auxiliary Boiler - Supplier Instrument List and Datasheets</t>
+          <t>Air Compressors and Dryers - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>ALP-M09-00QHA-ME-DSH-0001</t>
+          <t>ALP-M09-00QHA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -53832,14 +54041,14 @@
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Auxiliary Boiler - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Auxiliary Boiler - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>ALP-M10-00QJA-IC-DSH-0001</t>
+          <t>ALP-M09-00QHA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -53854,14 +54063,14 @@
       </c>
       <c r="D388" t="inlineStr">
         <is>
-          <t>Nitrogen, Hydrogen and CO2 Supply - Supplier Instrument List and Datasheets</t>
+          <t>Auxiliary Boiler - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>ALP-M10-00QJA-ME-DSH-0001</t>
+          <t>ALP-M10-00QJA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -53876,14 +54085,14 @@
       </c>
       <c r="D389" t="inlineStr">
         <is>
-          <t>Nitrogen, Hydrogen and CO2 Supply - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Nitrogen, Hydrogen and CO2 Supply - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>ALP-M11-00QCA-IC-DSH-0001</t>
+          <t>ALP-M10-00QJA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -53898,14 +54107,14 @@
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Chemical Dosing Skid - Supplier Instrument List and Datasheets</t>
+          <t>Nitrogen, Hydrogen and CO2 Supply - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ALP-M11-00QCA-ME-DSH-0001</t>
+          <t>ALP-M11-00QCA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -53920,14 +54129,14 @@
       </c>
       <c r="D391" t="inlineStr">
         <is>
-          <t>Chemical Dosing Skid - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Chemical Dosing Skid - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>ALP-M12-00GBA-IC-DSH-0001</t>
+          <t>ALP-M11-00QCA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -53942,14 +54151,14 @@
       </c>
       <c r="D392" t="inlineStr">
         <is>
-          <t>SWRO, demin, condensate polishing</t>
+          <t>Chemical Dosing Skid - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>ALP-M12-00GBA-ME-DSH-0001</t>
+          <t>ALP-M12-00GBA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -53971,7 +54180,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>ALP-M13-00GHA-IC-DSH-0001</t>
+          <t>ALP-M12-00GBA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -53986,14 +54195,14 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Shop-Built Tanks and Demin Forwarding Pumps - Supplier Instrument List and Datasheets</t>
+          <t>SWRO, demin, condensate polishing</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>ALP-M13-00GHA-ME-DSH-0001</t>
+          <t>ALP-M13-00GHA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -54008,14 +54217,14 @@
       </c>
       <c r="D395" t="inlineStr">
         <is>
-          <t>Shop-Built Tanks and Demin Forwarding Pumps - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Shop-Built Tanks and Demin Forwarding Pumps - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>ALP-M14-00GNA-IC-DSH-0001</t>
+          <t>ALP-M13-00GHA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -54030,14 +54239,14 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Waste Water and Sanitary Treatment Packages - Supplier Instrument List and Datasheets</t>
+          <t>Shop-Built Tanks and Demin Forwarding Pumps - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>ALP-M14-00GNA-ME-DSH-0001</t>
+          <t>ALP-M14-00GNA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -54052,14 +54261,14 @@
       </c>
       <c r="D397" t="inlineStr">
         <is>
-          <t>Waste Water and Sanitary Treatment Packages - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Waste Water and Sanitary Treatment Packages - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>ALP-M15-00EKA-IC-DSH-0001</t>
+          <t>ALP-M14-00GNA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -54074,14 +54283,14 @@
       </c>
       <c r="D398" t="inlineStr">
         <is>
-          <t>Gas Receiving and Metering Station - Supplier Instrument List and Datasheets</t>
+          <t>Waste Water and Sanitary Treatment Packages - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>ALP-M15-00EKA-ME-DSH-0001</t>
+          <t>ALP-M15-00EKA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -54096,14 +54305,14 @@
       </c>
       <c r="D399" t="inlineStr">
         <is>
-          <t>Gas Receiving and Metering Station - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Gas Receiving and Metering Station - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>ALP-M16-00EGA-IC-DSH-0001</t>
+          <t>ALP-M15-00EKA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -54118,14 +54327,14 @@
       </c>
       <c r="D400" t="inlineStr">
         <is>
-          <t>LDO Unloading and Forwarding / Treatment Skids - Supplier Instrument List and Datasheets</t>
+          <t>Gas Receiving and Metering Station - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>ALP-M16-00EGA-ME-DSH-0001</t>
+          <t>ALP-M16-00EGA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -54140,14 +54349,14 @@
       </c>
       <c r="D401" t="inlineStr">
         <is>
-          <t>LDO Unloading and Forwarding / Treatment Skids - Supplier Certified Datasheets and Performance Curves</t>
+          <t>LDO Unloading and Forwarding / Treatment Skids - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>ALP-M18-10HSB-IC-DSH-0001</t>
+          <t>ALP-M16-00EGA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -54162,14 +54371,14 @@
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Aqueous Ammonia Storage and Forwarding - Supplier Instrument List and Datasheets</t>
+          <t>LDO Unloading and Forwarding / Treatment Skids - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>ALP-M18-10HSB-ME-DSH-0001</t>
+          <t>ALP-M18-10HSB-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -54184,14 +54393,14 @@
       </c>
       <c r="D403" t="inlineStr">
         <is>
-          <t>Aqueous Ammonia Storage and Forwarding - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Aqueous Ammonia Storage and Forwarding - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>ALP-M19-10HAN-IC-DSH-0001</t>
+          <t>ALP-M18-10HSB-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -54206,14 +54415,14 @@
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>HRSG Blowdown and Drain Tanks - Supplier Instrument List and Datasheets</t>
+          <t>Aqueous Ammonia Storage and Forwarding - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>ALP-M19-10HAN-ME-DSH-0001</t>
+          <t>ALP-M19-10HAN-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -54228,14 +54437,14 @@
       </c>
       <c r="D405" t="inlineStr">
         <is>
-          <t>HRSG Blowdown and Drain Tanks - Supplier Certified Datasheets and Performance Curves</t>
+          <t>HRSG Blowdown and Drain Tanks - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>ALP-M20-00SGA-IC-DSH-0001</t>
+          <t>ALP-M19-10HAN-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -54250,14 +54459,14 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>Fire Pumps and Fire Protection Systems - Supplier Instrument List and Datasheets</t>
+          <t>HRSG Blowdown and Drain Tanks - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>ALP-M20-00SGA-ME-DSH-0001</t>
+          <t>ALP-M20-00SGA-IC-DSH-0001</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -54272,14 +54481,14 @@
       </c>
       <c r="D407" t="inlineStr">
         <is>
-          <t>Fire Pumps and Fire Protection Systems - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Fire Pumps and Fire Protection Systems - Supplier Instrument List and Datasheets</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ALP-M21-00SMA-ME-DSH-0001</t>
+          <t>ALP-M20-00SGA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -54294,14 +54503,14 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>EOT Cranes - Supplier Certified Datasheets and Performance Curves</t>
+          <t>Fire Pumps and Fire Protection Systems - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>ALP-P01-00000-ME-DSH-0001</t>
+          <t>ALP-M21-00SMA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -54316,14 +54525,14 @@
       </c>
       <c r="D409" t="inlineStr">
         <is>
-          <t>carbon steel, stainless</t>
+          <t>EOT Cranes - Supplier Certified Datasheets and Performance Curves</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>ALP-P02-10LBA-ME-DSH-0001</t>
+          <t>ALP-P01-00000-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -54338,14 +54547,14 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>main steam, reheat</t>
+          <t>carbon steel, stainless</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ALP-P03-00000-ME-DSH-0001</t>
+          <t>ALP-P02-10LBA-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -54360,14 +54569,14 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>manual and check</t>
+          <t>main steam, reheat</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>ALP-P04-00PAB-ME-DSH-0001</t>
+          <t>ALP-P03-00000-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -54382,14 +54591,14 @@
       </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>GRP CW Pipes and Fittings - Supplier Catalogues and Material Datasheets</t>
+          <t>manual and check</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>ALP-P05-00000-ME-DSH-0001</t>
+          <t>ALP-P04-00PAB-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -54404,14 +54613,14 @@
       </c>
       <c r="D413" t="inlineStr">
         <is>
-          <t>Pipe Supports, Spring Hangers and Snubbers - Supplier Catalogues and Material Datasheets</t>
+          <t>GRP CW Pipes and Fittings - Supplier Catalogues and Material Datasheets</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>ALP-P06-00000-ME-DSH-0001</t>
+          <t>ALP-P05-00000-ME-DSH-0001</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -54426,109 +54635,51 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>strainers, steam traps, expansion joints, sight glasses</t>
+          <t>Pipe Supports, Spring Hangers and Snubbers - Supplier Catalogues and Material Datasheets</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
+          <t>ALP-P06-00000-ME-DSH-0001</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>Specification Documents</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>strainers, steam traps, expansion joints, sight glasses</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
           <t>ALP-P07-00000-ME-DSH-0001</t>
         </is>
       </c>
-      <c r="B415" t="inlineStr">
-        <is>
-          <t>document</t>
-        </is>
-      </c>
-      <c r="C415" t="inlineStr">
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>document</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
         <is>
           <t>Specification Documents</t>
         </is>
       </c>
-      <c r="D415" t="inlineStr">
+      <c r="D416" t="inlineStr">
         <is>
           <t>Safety and Relief Valves - Supplier Catalogues and Material Datasheets</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AVEVA-1.0.1-CLA-001212</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>10HNE10</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Stack</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Stack 65 m, D 9.2 m, with silencer and CEMS platform</t>
         </is>
       </c>
     </row>
@@ -54579,7 +54730,7 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001230</t>
+          <t>AVEVA-1.0.1-CLA-001212</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -54593,7 +54744,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10HAA10</t>
+          <t>10HNE10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -54603,12 +54754,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steam Generator</t>
+          <t>Stack</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Heat recovery steam generator, 3-pressure reheat</t>
+          <t>Stack 65 m, D 9.2 m, with silencer and CEMS platform</t>
         </is>
       </c>
     </row>
@@ -54659,7 +54810,7 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001234</t>
+          <t>AVEVA-1.0.1-CLA-001230</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -54673,7 +54824,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20MAA10</t>
+          <t>10HAA10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -54683,12 +54834,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Steam Turbine</t>
+          <t>Steam Generator</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Steam turbine, reheat condensing, 2 casings</t>
+          <t>Heat recovery steam generator, 3-pressure reheat</t>
         </is>
       </c>
     </row>
@@ -54703,7 +54854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -54739,7 +54890,7 @@
       <c r="B2" s="2" t="inlineStr"/>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>AVEVA-1.0.1-CLA-001260</t>
+          <t>AVEVA-1.0.1-CLA-001234</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr"/>
@@ -54753,7 +54904,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>00ACA10</t>
+          <t>20MAA10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -54763,452 +54914,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switchgear And Controlgear</t>
+          <t>Steam Turbine</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>380 kV GIS, double busbar, 6 bays</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00BBA10</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>MV switchgear 10.5 kV, section A</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00BBA20</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>MV switchgear 10.5 kV, section B</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00BFA10</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LV main switchboard 0.4 kV, A</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00BFA20</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>LV main switchboard 0.4 kV, B</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00BFA30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LV MCC - power block</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00BFA40</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>LV MCC - CW pump house</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00BFA50</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>LV MCC - water treatment</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00BFA60</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>LV MCC - BOP utilities</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>00BFA70</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>LV MCC - fuel gas and LDO</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>00BFA80</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LV MCC - buildings and HVAC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>00BMA10</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Emergency LV switchboard</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>00BMA20</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Emergency MCC - power block</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>00BRA20</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>DC 220 V distribution board</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>10BAA10</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>GT isolated phase busduct</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>10BAC10</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>GT generator circuit breaker</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>10MKC10</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>GT static excitation</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>10MKC20</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>GT static frequency converter</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>20BAA10</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ST isolated phase busduct</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>20BAC10</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>ST generator circuit breaker</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>20MKC10</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Switchgear And Controlgear</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ST static excitation</t>
+          <t>Steam turbine, reheat condensing, 2 casings</t>
         </is>
       </c>
     </row>
@@ -55218,6 +54929,614 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001260</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00ACA10</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>380 kV GIS, double busbar, 6 bays</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00BBA10</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>MV switchgear 10.5 kV, section A</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00BBA20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MV switchgear 10.5 kV, section B</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00BFA10</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - GT and HRSG, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00BFA11</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - ST and cooling, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00BFA12</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - BOP, fuel and buildings, A</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00BFA20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - GT and HRSG, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00BFA21</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - ST and cooling, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00BFA22</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LV main switchboard 0.42 kV - BOP, fuel and buildings, B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00BFA30</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LV MCC - power block</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00BFA40</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LV MCC - CW pump house</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00BFA50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LV MCC - water treatment</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00BFA60</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LV MCC - BOP utilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00BFA70</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LV MCC - fuel gas and LDO</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00BFA80</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LV MCC - buildings and HVAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00BMA10</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Emergency LV switchboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00BMA20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Emergency MCC - power block</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00BRA20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DC 220 V distribution board</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>10BAA10</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>GT isolated phase busduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10BAC10</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>GT generator circuit breaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10MKC10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>GT static excitation</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10MKC20</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>GT static frequency converter</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>20BAA10</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>ST isolated phase busduct</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20BAC10</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ST generator circuit breaker</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>20MKC10</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Switchgear And Controlgear</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>ST static excitation</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -55341,7 +55660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -58009,702 +58328,6 @@
       <c r="D122" t="inlineStr">
         <is>
           <t>Steam turbine hall</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D32"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Entity</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Class</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-      <c r="B2" s="2" t="inlineStr"/>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>AVEVA-1.0.1-CLA-001272</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr"/>
-      <c r="B3" s="2" t="inlineStr"/>
-      <c r="C3" s="2" t="inlineStr"/>
-      <c r="D3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>00EGA10BB001</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LDO unloading slop tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>00EGB10BB003</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>LDO tank farm recovery sump</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>00EKA10BB001</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Gas station condensate drain vessel</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>00GBA10BB001</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>SWRO permeate tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>00GHA10BB001</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Demineralised water tank A</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>00GHA10BB002</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Demineralised water tank B</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>00GKA10BB001</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Potable water tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>00GMA10BB001</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Neutralisation pit</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>00GNA10BB001</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Equalisation tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>00GNA10BB002</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Neutralisation tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>00GNA10BB003</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Sulphuric acid tank (neutralisation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>00GNA10BB004</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Caustic tank (neutralisation)</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>00PBA10BB001</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Hypochlorite storage tank A</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>00PBA10BB002</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Hypochlorite storage tank B</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>00PGA10BB002</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CCW chemical pot feeder</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>00QCA10BB001</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Ammonia solution tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>00QCA10BB002</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Oxygen scavenger tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>00QCA10BB003</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Caustic solution tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>00QEA10BB002</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Service air receiver</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>00QHA10BB001</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Auxiliary boiler feed water tank / deaerator</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>00QHA10BB002</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Auxiliary boiler blowdown vessel</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>00QJA10BB001</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nitrogen buffer vessel</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>00SGA10BB002</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Fire water tank B</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>00SGC10BB001</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Foam concentrate tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>00XJA10BB001</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Emergency diesel generator day tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>10HAN10BB001</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>HRSG blowdown tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>10HAN10BB002</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Atmospheric drain tank</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>10HSB10BB001</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Aqueous ammonia tank A 30 m3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>10HSB10BB002</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>equipment</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Tank</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Aqueous ammonia tank B 30 m3</t>
         </is>
       </c>
     </row>
@@ -58799,6 +58422,848 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D32"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001272</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>00EGA10BB001</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LDO unloading slop tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>00EGB10BB003</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LDO tank farm recovery sump</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>00EKA10BB001</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Gas station condensate drain vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>00GBA10BB001</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>SWRO permeate tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>00GHA10BB001</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Demineralised water tank A</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>00GHA10BB002</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Demineralised water tank B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>00GKA10BB001</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Potable water tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>00GMA10BB001</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Neutralisation pit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>00GNA10BB001</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Equalisation tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>00GNA10BB002</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Neutralisation tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>00GNA10BB003</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Sulphuric acid tank (neutralisation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>00GNA10BB004</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Caustic tank (neutralisation)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>00PBA10BB001</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Hypochlorite storage tank A</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>00PBA10BB002</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Hypochlorite storage tank B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>00PGA10BB002</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CCW chemical pot feeder</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>00QCA10BB001</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ammonia solution tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>00QCA10BB002</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Oxygen scavenger tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>00QCA10BB003</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Caustic solution tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>00QEA10BB002</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Service air receiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>00QHA10BB001</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Auxiliary boiler feed water tank / deaerator</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>00QHA10BB002</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Auxiliary boiler blowdown vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>00QJA10BB001</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Nitrogen buffer vessel</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>00SGA10BB002</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Fire water tank B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>00SGC10BB001</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Foam concentrate tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>00XJA10BB001</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Emergency diesel generator day tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>10HAN10BB001</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>HRSG blowdown tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>10HAN10BB002</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Atmospheric drain tank</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>10HSB10BB001</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Aqueous ammonia tank A 30 m3</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>10HSB10BB002</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Aqueous ammonia tank B 30 m3</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001318</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10MKA20</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>GT generator neutral earthing transformer</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10MKC30</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>GT excitation transformer</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>20MKA20</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>ST generator neutral earthing transformer</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>20MKC20</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ST excitation transformer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -58865,6 +59330,130 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>UPS 230 V AC (2 x 100 %)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Class</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr"/>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>AVEVA-1.0.1-CLA-001471</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr"/>
+      <c r="B3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="inlineStr"/>
+      <c r="D3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>10LBA10AA501</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>HP bypass valve (to cold reheat)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>10LBB10AA501</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>IP bypass valve (to condenser)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>10LBD10AA501</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Valve</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LP bypass valve (to condenser)</t>
         </is>
       </c>
     </row>
@@ -59325,7 +59914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D72"/>
+  <dimension ref="A1:D74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -60673,7 +61262,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10HAN10AP001</t>
+          <t>10HAA10AP001</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -60688,14 +61277,14 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>HRSG drain pump A</t>
+          <t>HRSG condensate preheater recirculation pump A</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10HAN10AP002</t>
+          <t>10HAA10AP002</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -60710,14 +61299,14 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>HRSG drain pump B</t>
+          <t>HRSG condensate preheater recirculation pump B</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10HSB10AP001</t>
+          <t>10HAN10AP001</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -60732,14 +61321,14 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Ammonia forwarding pump A</t>
+          <t>HRSG drain pump A</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10HSB10AP002</t>
+          <t>10HAN10AP002</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -60754,14 +61343,14 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Ammonia forwarding pump B</t>
+          <t>HRSG drain pump B</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10LAC10AP001</t>
+          <t>10HSB10AP001</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -60776,14 +61365,14 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Boiler feed pump A (2 x 100 %, VFD)</t>
+          <t>Ammonia forwarding pump A</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10LAC10AP002</t>
+          <t>10HSB10AP002</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -60798,14 +61387,14 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Boiler feed pump B (2 x 100 %, VFD)</t>
+          <t>Ammonia forwarding pump B</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>20LCB10AP001</t>
+          <t>10LAC10AP001</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -60820,14 +61409,14 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Condensate extraction pump A (2 x 100 %)</t>
+          <t>Boiler feed pump A (2 x 100 %, VFD)</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>20LCB10AP002</t>
+          <t>10LAC10AP002</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -60842,14 +61431,14 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Condensate extraction pump B (2 x 100 %)</t>
+          <t>Boiler feed pump B (2 x 100 %, VFD)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>20MAJ10AP001</t>
+          <t>20LCB10AP001</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -60864,27 +61453,71 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Condenser vacuum pump A</t>
+          <t>Condensate extraction pump A (2 x 100 %)</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>20LCB10AP002</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Condensate extraction pump B (2 x 100 %)</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>20MAJ10AP001</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>equipment</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Condenser vacuum pump A</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
           <t>20MAJ10AP002</t>
         </is>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B74" t="inlineStr">
         <is>
           <t>equipment</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
+      <c r="C74" t="inlineStr">
         <is>
           <t>Centrifugal Pump</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
+      <c r="D74" t="inlineStr">
         <is>
           <t>Condenser vacuum pump B</t>
         </is>
